--- a/merged_b2_full_cypress_coverage.xlsx
+++ b/merged_b2_full_cypress_coverage.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K677"/>
+  <dimension ref="A1:K678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -21514,17 +21514,17 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>santander</t>
+          <t>sanlam</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>EftDebitOrder</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -21569,7 +21569,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>PixAutomaticoPush</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -21619,17 +21619,17 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
@@ -21659,22 +21659,22 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>PixAutomaticoQr</t>
+          <t>PixAutomaticoPush</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
@@ -21709,17 +21709,17 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
@@ -21744,27 +21744,27 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Voucher</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>PixAutomaticoQr</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
@@ -21784,17 +21784,17 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>shift4</t>
+          <t>santander</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Voucher</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Eps</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -21814,7 +21814,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -21839,7 +21839,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>Eps</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -21884,7 +21884,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -21929,7 +21929,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Sofort</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -21969,12 +21969,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Sofort</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -22019,7 +22019,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -22054,7 +22054,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>silverflow</t>
+          <t>shift4</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -22144,7 +22144,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>silverflow</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -22234,17 +22234,17 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>stax</t>
+          <t>square</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>BankDebit</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Ach</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -22284,12 +22284,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Ach</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -22309,7 +22309,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -22369,17 +22369,17 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>stax</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>BankDebit</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Ach</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -22399,7 +22399,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -22429,17 +22429,17 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
@@ -22469,22 +22469,22 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Bacs</t>
+          <t>Ach</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
@@ -22519,17 +22519,17 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
@@ -22559,22 +22559,22 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Becs</t>
+          <t>Bacs</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
@@ -22609,17 +22609,17 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
@@ -22649,22 +22649,22 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Sepa</t>
+          <t>Becs</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
@@ -22699,17 +22699,17 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
@@ -22734,44 +22734,40 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>BancontactCard</t>
+          <t>Sepa</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I491" t="inlineStr">
-        <is>
-          <t>2026-04-20 22:45:07</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr"/>
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr"/>
     </row>
@@ -22793,22 +22789,22 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -22837,35 +22833,39 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Blik</t>
+          <t>BancontactCard</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I493" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:45:07</t>
+        </is>
+      </c>
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr"/>
     </row>
@@ -22882,7 +22882,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Eps</t>
+          <t>Blik</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -22927,7 +22927,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>Eps</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -22972,7 +22972,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -23022,22 +23022,22 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -23062,27 +23062,27 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>OnlineBankingFpx</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -23107,7 +23107,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Przelewy24</t>
+          <t>OnlineBankingFpx</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -23152,7 +23152,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Sofort</t>
+          <t>Przelewy24</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -23202,22 +23202,22 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -23237,32 +23237,32 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Ach</t>
+          <t>Sofort</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -23287,7 +23287,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Bacs</t>
+          <t>Ach</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -23332,7 +23332,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Multibanco</t>
+          <t>Bacs</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -23377,7 +23377,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>SepaBankTransfer</t>
+          <t>Multibanco</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -23417,12 +23417,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>SepaBankTransfer</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -23447,14 +23447,10 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I506" t="inlineStr">
-        <is>
-          <t>2026-04-21 1:34:33</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr"/>
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr"/>
     </row>
@@ -23476,17 +23472,17 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
@@ -23501,7 +23497,7 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>2026-04-20 16:54:39</t>
+          <t>2026-04-21 1:34:33</t>
         </is>
       </c>
       <c r="J507" t="inlineStr"/>
@@ -23520,22 +23516,22 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
@@ -23550,7 +23546,7 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>2026-04-21 1:38:16</t>
+          <t>2026-04-20 16:54:39</t>
         </is>
       </c>
       <c r="J508" t="inlineStr"/>
@@ -23574,17 +23570,17 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
@@ -23599,7 +23595,7 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>2026-04-20 10:53:25</t>
+          <t>2026-04-21 1:38:16</t>
         </is>
       </c>
       <c r="J509" t="inlineStr"/>
@@ -23613,32 +23609,32 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>PayLater</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -23648,7 +23644,7 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>2026-04-21 1:37:45</t>
+          <t>2026-04-20 10:53:25</t>
         </is>
       </c>
       <c r="J510" t="inlineStr"/>
@@ -23667,7 +23663,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>AfterpayClearpay</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -23692,10 +23688,14 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I511" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>2026-04-21 1:37:45</t>
+        </is>
+      </c>
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr"/>
     </row>
@@ -23712,7 +23712,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Klarna</t>
+          <t>AfterpayClearpay</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -23737,14 +23737,10 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I512" t="inlineStr">
-        <is>
-          <t>2026-04-21 1:36:26</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr"/>
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr"/>
     </row>
@@ -23756,12 +23752,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>PayLater</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>AliPay</t>
+          <t>Klarna</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -23786,10 +23782,14 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I513" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>2026-04-21 1:36:26</t>
+        </is>
+      </c>
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr"/>
     </row>
@@ -23806,7 +23806,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>AmazonPay</t>
+          <t>AliPay</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -23856,17 +23856,17 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
@@ -23896,22 +23896,22 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>AmazonPay</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
@@ -23946,17 +23946,17 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
@@ -23986,22 +23986,22 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Cashapp</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
@@ -24036,17 +24036,17 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
@@ -24076,22 +24076,22 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Cashapp</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
@@ -24126,17 +24126,17 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
@@ -24166,22 +24166,22 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>RevolutPay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
@@ -24216,17 +24216,17 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
@@ -24256,22 +24256,22 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>WeChatPay</t>
+          <t>RevolutPay</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
@@ -24291,17 +24291,17 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>tesouro</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>WeChatPay</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -24321,7 +24321,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -24351,17 +24351,17 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
@@ -24391,22 +24391,22 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
@@ -24441,17 +24441,17 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
@@ -24476,32 +24476,32 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -24531,17 +24531,17 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
@@ -24571,22 +24571,22 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
@@ -24621,17 +24621,17 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -24651,37 +24651,37 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>tokenio</t>
+          <t>tesouro</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>OpenBanking</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>OpenBankingPIS</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -24696,17 +24696,17 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>truelayer</t>
+          <t>tokenio</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>OpenBanking</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>OpenBanking</t>
+          <t>OpenBankingPIS</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -24741,7 +24741,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>trustly</t>
+          <t>truelayer</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -24751,7 +24751,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Trustly</t>
+          <t>OpenBanking</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -24786,7 +24786,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>trustpay</t>
+          <t>trustly</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -24796,7 +24796,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Blik</t>
+          <t>Trustly</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -24816,7 +24816,7 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -24841,7 +24841,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Eps</t>
+          <t>Blik</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -24866,14 +24866,10 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I537" t="inlineStr">
-        <is>
-          <t>2026-04-21 0:07:05</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr"/>
       <c r="J537" t="inlineStr"/>
       <c r="K537" t="inlineStr"/>
     </row>
@@ -24890,7 +24886,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>Eps</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -24915,10 +24911,14 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I538" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>2026-04-21 0:07:05</t>
+        </is>
+      </c>
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr"/>
     </row>
@@ -24935,7 +24935,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -24960,14 +24960,10 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I539" t="inlineStr">
-        <is>
-          <t>2026-04-19 23:12:22</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr"/>
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr"/>
     </row>
@@ -24984,7 +24980,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Sofort</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -25009,10 +25005,14 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I540" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>2026-04-19 23:12:22</t>
+        </is>
+      </c>
       <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr"/>
     </row>
@@ -25024,12 +25024,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>InstantBankTransfer</t>
+          <t>Sofort</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>InstantBankTransferFinland</t>
+          <t>InstantBankTransfer</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -25119,7 +25119,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>InstantBankTransferPoland</t>
+          <t>InstantBankTransferFinland</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -25164,7 +25164,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>SepaBankTransfer</t>
+          <t>InstantBankTransferPoland</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -25189,14 +25189,10 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I544" t="inlineStr">
-        <is>
-          <t>2026-04-20 23:47:16</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr"/>
       <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr"/>
     </row>
@@ -25208,12 +25204,12 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>SepaBankTransfer</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -25243,7 +25239,7 @@
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>2026-04-21 0:08:32</t>
+          <t>2026-04-20 23:47:16</t>
         </is>
       </c>
       <c r="J545" t="inlineStr"/>
@@ -25262,7 +25258,7 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -25292,7 +25288,7 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>2026-04-21 1:17:59</t>
+          <t>2026-04-21 0:08:32</t>
         </is>
       </c>
       <c r="J546" t="inlineStr"/>
@@ -25306,12 +25302,12 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>NetworkToken</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>NetworkToken</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -25336,10 +25332,14 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I547" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>2026-04-21 1:17:59</t>
+        </is>
+      </c>
       <c r="J547" t="inlineStr"/>
       <c r="K547" t="inlineStr"/>
     </row>
@@ -25351,12 +25351,12 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>NetworkToken</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>NetworkToken</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -25376,19 +25376,15 @@
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I548" t="inlineStr">
-        <is>
-          <t>2026-04-21 1:01:59</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr"/>
       <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr"/>
     </row>
@@ -25405,7 +25401,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -25435,7 +25431,7 @@
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>2026-04-20 20:43:18</t>
+          <t>2026-04-21 1:01:59</t>
         </is>
       </c>
       <c r="J549" t="inlineStr"/>
@@ -25444,17 +25440,17 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>trustpayments</t>
+          <t>trustpay</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -25474,15 +25470,19 @@
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I550" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:43:18</t>
+        </is>
+      </c>
       <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr"/>
     </row>
@@ -25499,7 +25499,7 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -25534,7 +25534,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>tsys</t>
+          <t>trustpayments</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -25544,7 +25544,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -25589,7 +25589,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -25624,17 +25624,17 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>tsys</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>OpenBanking</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -25679,7 +25679,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>OpenBankingUk</t>
+          <t>OpenBanking</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -25714,17 +25714,17 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>wellsfargo</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>BankDebit</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Ach</t>
+          <t>OpenBankingUk</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
@@ -25744,7 +25744,7 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -25764,12 +25764,12 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Ach</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -25789,7 +25789,7 @@
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -25819,17 +25819,17 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
@@ -25859,22 +25859,22 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
@@ -25909,17 +25909,17 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
@@ -25944,32 +25944,32 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -25999,17 +25999,17 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
@@ -26039,22 +26039,22 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
@@ -26089,17 +26089,17 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
@@ -26119,37 +26119,37 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>worldline</t>
+          <t>wellsfargo</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -26174,7 +26174,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -26214,12 +26214,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -26299,7 +26299,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>worldpay</t>
+          <t>worldline</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -26309,7 +26309,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -26329,19 +26329,15 @@
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I569" t="inlineStr">
-        <is>
-          <t>2026-04-21 0:59:53</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr"/>
       <c r="J569" t="inlineStr"/>
       <c r="K569" t="inlineStr"/>
     </row>
@@ -26363,17 +26359,17 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
@@ -26383,10 +26379,14 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I570" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>2026-04-21 0:59:53</t>
+        </is>
+      </c>
       <c r="J570" t="inlineStr"/>
       <c r="K570" t="inlineStr"/>
     </row>
@@ -26403,22 +26403,22 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
@@ -26428,14 +26428,10 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I571" t="inlineStr">
-        <is>
-          <t>2026-04-20 8:06:33</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr"/>
       <c r="J571" t="inlineStr"/>
       <c r="K571" t="inlineStr"/>
     </row>
@@ -26457,17 +26453,17 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
@@ -26477,10 +26473,14 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I572" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>2026-04-20 8:06:33</t>
+        </is>
+      </c>
       <c r="J572" t="inlineStr"/>
       <c r="K572" t="inlineStr"/>
     </row>
@@ -26492,44 +26492,40 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I573" t="inlineStr">
-        <is>
-          <t>2026-04-19 4:54:56</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr"/>
       <c r="J573" t="inlineStr"/>
       <c r="K573" t="inlineStr"/>
     </row>
@@ -26546,7 +26542,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -26576,7 +26572,7 @@
       </c>
       <c r="I574" t="inlineStr">
         <is>
-          <t>2026-04-19 16:49:10</t>
+          <t>2026-04-19 4:54:56</t>
         </is>
       </c>
       <c r="J574" t="inlineStr"/>
@@ -26585,7 +26581,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>worldpaymodular</t>
+          <t>worldpay</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -26595,7 +26591,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -26615,7 +26611,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -26625,7 +26621,7 @@
       </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t>2026-01-21 11:49:57</t>
+          <t>2026-04-19 16:49:10</t>
         </is>
       </c>
       <c r="J575" t="inlineStr"/>
@@ -26649,17 +26645,17 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -26669,10 +26665,14 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I576" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>2026-01-21 11:49:57</t>
+        </is>
+      </c>
       <c r="J576" t="inlineStr"/>
       <c r="K576" t="inlineStr"/>
     </row>
@@ -26689,22 +26689,22 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
@@ -26714,14 +26714,10 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I577" t="inlineStr">
-        <is>
-          <t>2026-01-21 12:08:57</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr"/>
       <c r="J577" t="inlineStr"/>
       <c r="K577" t="inlineStr"/>
     </row>
@@ -26743,17 +26739,17 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
@@ -26763,47 +26759,51 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I578" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>2026-01-21 12:08:57</t>
+        </is>
+      </c>
       <c r="J578" t="inlineStr"/>
       <c r="K578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>worldpayvantiv</t>
+          <t>worldpaymodular</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -26833,17 +26833,17 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
@@ -26873,22 +26873,22 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
@@ -26923,17 +26923,17 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
@@ -26963,22 +26963,22 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
@@ -27013,17 +27013,17 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
@@ -27048,32 +27048,32 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
@@ -27103,17 +27103,17 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
@@ -27143,22 +27143,22 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
@@ -27193,17 +27193,17 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
@@ -27223,49 +27223,45 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>worldpayxml</t>
+          <t>worldpayvantiv</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I589" t="inlineStr">
-        <is>
-          <t>2026-04-21 0:46:51</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr"/>
       <c r="J589" t="inlineStr"/>
       <c r="K589" t="inlineStr"/>
     </row>
@@ -27282,7 +27278,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -27312,7 +27308,7 @@
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>2026-04-20 12:19:30</t>
+          <t>2026-04-21 0:46:51</t>
         </is>
       </c>
       <c r="J590" t="inlineStr"/>
@@ -27326,12 +27322,12 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -27351,7 +27347,7 @@
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
@@ -27361,7 +27357,7 @@
       </c>
       <c r="I591" t="inlineStr">
         <is>
-          <t>2026-03-20 14:37:20</t>
+          <t>2026-04-20 12:19:30</t>
         </is>
       </c>
       <c r="J591" t="inlineStr"/>
@@ -27385,17 +27381,17 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
@@ -27405,10 +27401,14 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I592" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:37:20</t>
+        </is>
+      </c>
       <c r="J592" t="inlineStr"/>
       <c r="K592" t="inlineStr"/>
     </row>
@@ -27425,22 +27425,22 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
@@ -27450,14 +27450,10 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I593" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:38:54</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr"/>
       <c r="J593" t="inlineStr"/>
       <c r="K593" t="inlineStr"/>
     </row>
@@ -27479,17 +27475,17 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
@@ -27499,47 +27495,51 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I594" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:38:54</t>
+        </is>
+      </c>
       <c r="J594" t="inlineStr"/>
       <c r="K594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>xendit</t>
+          <t>worldpayxml</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -27569,17 +27569,17 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
@@ -27609,22 +27609,22 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
@@ -27659,17 +27659,17 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
@@ -27694,32 +27694,32 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>RealTimePayment</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Qris</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -27749,17 +27749,17 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
@@ -27779,37 +27779,37 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>zen</t>
+          <t>xendit</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>RealTimePayment</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Multibanco</t>
+          <t>Qris</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -27834,7 +27834,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Multibanco</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -27879,7 +27879,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Pse</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -27919,12 +27919,12 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Pse</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -27969,7 +27969,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -28009,12 +28009,12 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Voucher</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -28059,7 +28059,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Efecty</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -28104,7 +28104,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>PagoEfectivo</t>
+          <t>Efecty</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -28149,7 +28149,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>RedCompra</t>
+          <t>PagoEfectivo</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -28194,7 +28194,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>RedPagos</t>
+          <t>RedCompra</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -28234,12 +28234,12 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Voucher</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>RedPagos</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -28284,7 +28284,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -28319,17 +28319,17 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>zift</t>
+          <t>zen</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -28349,19 +28349,15 @@
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I613" t="inlineStr">
-        <is>
-          <t>2026-04-20 2:16:52</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr"/>
       <c r="J613" t="inlineStr"/>
       <c r="K613" t="inlineStr"/>
     </row>
@@ -28383,17 +28379,17 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
@@ -28403,10 +28399,14 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I614" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>2026-04-20 2:16:52</t>
+        </is>
+      </c>
       <c r="J614" t="inlineStr"/>
       <c r="K614" t="inlineStr"/>
     </row>
@@ -28423,22 +28423,22 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
@@ -28448,14 +28448,10 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I615" t="inlineStr">
-        <is>
-          <t>2026-04-20 20:57:09</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr"/>
       <c r="J615" t="inlineStr"/>
       <c r="K615" t="inlineStr"/>
     </row>
@@ -28477,17 +28473,17 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
@@ -28497,47 +28493,51 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I616" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:57:09</t>
+        </is>
+      </c>
       <c r="J616" t="inlineStr"/>
       <c r="K616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>zsl</t>
+          <t>zift</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>LocalBankTransfer</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -28552,42 +28552,42 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>adyen</t>
+          <t>zsl</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>LocalBankTransfer</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>Payment (Decrypt Flow)</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>HS pre-decrypts the wallet token and sends plaintext card data to the connector instead of the encrypted blob</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="I618" t="inlineStr"/>
@@ -28607,7 +28607,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -28622,7 +28622,7 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
@@ -28652,7 +28652,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -28667,7 +28667,7 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
@@ -28687,7 +28687,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>archipel</t>
+          <t>adyen</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -28697,7 +28697,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -28712,12 +28712,12 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>bankofamerica</t>
+          <t>archipel</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -28787,7 +28787,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -28802,7 +28802,7 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
@@ -28832,7 +28832,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
@@ -28847,7 +28847,7 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
@@ -28867,7 +28867,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>barclaycard</t>
+          <t>bankofamerica</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -28877,7 +28877,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -28892,7 +28892,7 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
@@ -28922,7 +28922,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -28937,7 +28937,7 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
@@ -28967,7 +28967,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -28982,7 +28982,7 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
@@ -29002,7 +29002,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>braintree</t>
+          <t>barclaycard</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -29012,7 +29012,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
@@ -29057,7 +29057,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
@@ -29072,7 +29072,7 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
@@ -29102,7 +29102,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -29117,7 +29117,7 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
@@ -29137,7 +29137,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>braintree</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -29147,7 +29147,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -29162,7 +29162,7 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
@@ -29192,7 +29192,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -29207,7 +29207,7 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
@@ -29237,7 +29237,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -29252,7 +29252,7 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
@@ -29272,7 +29272,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>cybersource</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -29297,7 +29297,7 @@
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
@@ -29327,7 +29327,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -29342,7 +29342,7 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
@@ -29372,7 +29372,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -29387,7 +29387,7 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
@@ -29407,7 +29407,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>finix</t>
+          <t>cybersource</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -29417,7 +29417,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -29432,7 +29432,7 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
@@ -29477,7 +29477,7 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
@@ -29507,7 +29507,7 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -29522,7 +29522,7 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
@@ -29542,7 +29542,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>fiserv</t>
+          <t>finix</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -29567,7 +29567,7 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
@@ -29587,7 +29587,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>fiuu</t>
+          <t>fiserv</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -29642,7 +29642,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -29657,7 +29657,7 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
@@ -29687,7 +29687,7 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -29702,7 +29702,7 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
@@ -29722,7 +29722,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>gocardless</t>
+          <t>fiuu</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -29732,7 +29732,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
@@ -29747,12 +29747,12 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -29777,7 +29777,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -29792,7 +29792,7 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
@@ -29822,7 +29822,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -29837,7 +29837,7 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
@@ -29857,7 +29857,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>hipay</t>
+          <t>gocardless</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -29867,7 +29867,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -29882,12 +29882,12 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
@@ -29927,7 +29927,7 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
@@ -29957,7 +29957,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -29972,7 +29972,7 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
@@ -29992,7 +29992,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>mollie</t>
+          <t>hipay</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -30002,7 +30002,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
@@ -30017,7 +30017,7 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -30047,7 +30047,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -30062,7 +30062,7 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
@@ -30092,7 +30092,7 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -30107,7 +30107,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
@@ -30127,7 +30127,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>nmi</t>
+          <t>mollie</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -30137,7 +30137,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -30152,7 +30152,7 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
@@ -30182,7 +30182,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -30197,7 +30197,7 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
@@ -30227,7 +30227,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
@@ -30242,7 +30242,7 @@
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
@@ -30262,7 +30262,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>nuvei</t>
+          <t>nmi</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -30272,7 +30272,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -30287,7 +30287,7 @@
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -30332,7 +30332,7 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
@@ -30352,7 +30352,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>payme</t>
+          <t>nuvei</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -30362,7 +30362,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -30377,12 +30377,12 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -30407,7 +30407,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
@@ -30422,7 +30422,7 @@
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
@@ -30452,7 +30452,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -30467,7 +30467,7 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
@@ -30487,7 +30487,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>paysafe</t>
+          <t>payme</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -30497,7 +30497,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -30512,12 +30512,12 @@
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>paysafe</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -30587,7 +30587,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -30602,7 +30602,7 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
@@ -30632,7 +30632,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -30647,7 +30647,7 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
@@ -30667,7 +30667,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>stax</t>
+          <t>square</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -30677,7 +30677,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -30692,7 +30692,7 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
@@ -30722,7 +30722,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -30737,7 +30737,7 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
@@ -30782,7 +30782,7 @@
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
@@ -30802,7 +30802,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>stax</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -30812,7 +30812,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -30827,7 +30827,7 @@
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
@@ -30857,7 +30857,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -30872,7 +30872,7 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
@@ -30902,7 +30902,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -30917,7 +30917,7 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
@@ -30937,7 +30937,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>tesouro</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -30947,7 +30947,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -30962,7 +30962,7 @@
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
@@ -31007,7 +31007,7 @@
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
@@ -31027,7 +31027,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>wellsfargo</t>
+          <t>tesouro</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -31037,7 +31037,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -31052,7 +31052,7 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
@@ -31082,7 +31082,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -31097,7 +31097,7 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
@@ -31127,7 +31127,7 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -31142,7 +31142,7 @@
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
@@ -31162,7 +31162,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>worldpayvantiv</t>
+          <t>wellsfargo</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -31172,7 +31172,7 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -31187,7 +31187,7 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
@@ -31217,7 +31217,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -31232,7 +31232,7 @@
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
@@ -31248,6 +31248,51 @@
       <c r="I677" t="inlineStr"/>
       <c r="J677" t="inlineStr"/>
       <c r="K677" t="inlineStr"/>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>worldpayvantiv</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>GooglePay</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Payment (Decrypt Flow)</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>HS pre-decrypts the wallet token and sends plaintext card data to the connector instead of the encrypted blob</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>not_covered</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr"/>
+      <c r="J678" t="inlineStr"/>
+      <c r="K678" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
